--- a/Sample_Project/設計書/A1_プロジェクト管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(画面)_WA10301_TOPメニュー.xlsx
+++ b/Sample_Project/設計書/A1_プロジェクト管理システム/030_アプリ設計/110_テスト仕様書/単体テスト仕様書(画面)_WA10301_TOPメニュー.xlsx
@@ -13593,8 +13593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -13635,8 +13635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -13671,8 +13671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -13709,8 +13709,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -13743,8 +13743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -13777,8 +13777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -13811,8 +13811,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -13845,8 +13845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -13883,8 +13883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -13917,8 +13917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -13951,8 +13951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -13987,8 +13987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -14021,8 +14021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -14055,8 +14055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -14089,8 +14089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -14127,8 +14127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -14161,8 +14161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -14199,8 +14199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -14233,8 +14233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -14269,8 +14269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -14303,8 +14303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -14337,8 +14337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -14371,8 +14371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -14407,8 +14407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -14441,8 +14441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -14477,8 +14477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -14517,8 +14517,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -14551,8 +14551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -14585,8 +14585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -14619,8 +14619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -14657,8 +14657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -14691,8 +14691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -14733,8 +14733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -14767,8 +14767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -14801,8 +14801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -14837,8 +14837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -14871,8 +14871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -14905,8 +14905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -14941,8 +14941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -14975,8 +14975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -15011,8 +15011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -15045,8 +15045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -15079,8 +15079,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -15113,8 +15113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -15147,8 +15147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -15181,8 +15181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -15217,8 +15217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -15253,8 +15253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -15289,8 +15289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -15327,8 +15327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -15361,8 +15361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -15395,8 +15395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -15429,8 +15429,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -15463,8 +15463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -15499,8 +15499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -15533,8 +15533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -15567,8 +15567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -15601,8 +15601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -15635,8 +15635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -15669,8 +15669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -15703,8 +15703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -15737,8 +15737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -15773,8 +15773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -15809,8 +15809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -15843,8 +15843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -15877,8 +15877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -15911,8 +15911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -15945,8 +15945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -15985,8 +15985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -16019,8 +16019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -16055,8 +16055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -16091,8 +16091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -16125,8 +16125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -16161,8 +16161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -16197,8 +16197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -16237,8 +16237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -16273,8 +16273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -16309,8 +16309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -16349,8 +16349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -16383,8 +16383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -16419,8 +16419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -16455,8 +16455,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -16489,8 +16489,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -16525,8 +16525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -16565,8 +16565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -16599,8 +16599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -16633,8 +16633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -16667,8 +16667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -16701,8 +16701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -16737,8 +16737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -16771,8 +16771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -16805,8 +16805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -16839,8 +16839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -16873,8 +16873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -16909,8 +16909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -16951,8 +16951,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -16991,8 +16991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -17025,8 +17025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -17065,8 +17065,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -17105,8 +17105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -17139,8 +17139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -17181,8 +17181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -17217,8 +17217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -17251,8 +17251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -17285,8 +17285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -17321,8 +17321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -17355,8 +17355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -17389,8 +17389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -17423,8 +17423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -17457,8 +17457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -17493,8 +17493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -17527,8 +17527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -17561,8 +17561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -17595,8 +17595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -17629,8 +17629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -17665,8 +17665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -17703,8 +17703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -17743,8 +17743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -17779,8 +17779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -17813,8 +17813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -17847,8 +17847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -17889,8 +17889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -17925,8 +17925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -17959,8 +17959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -17993,8 +17993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -18029,8 +18029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -18063,8 +18063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -18101,8 +18101,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -18141,8 +18141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -18177,8 +18177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -18213,8 +18213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -18249,8 +18249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -18285,8 +18285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -18321,8 +18321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -18355,8 +18355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -18389,8 +18389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -18423,8 +18423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -18457,8 +18457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -18491,8 +18491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -18529,8 +18529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -18563,8 +18563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -18599,8 +18599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -18633,8 +18633,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -18667,8 +18667,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -18701,8 +18701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -18735,8 +18735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -18769,8 +18769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -18803,8 +18803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -18837,8 +18837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -18871,8 +18871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -18905,8 +18905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -18939,8 +18939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -18975,8 +18975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -19009,8 +19009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -19043,8 +19043,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -19077,8 +19077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -19111,8 +19111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -19145,8 +19145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -19179,8 +19179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -19215,8 +19215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -19249,8 +19249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -19283,8 +19283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -19317,8 +19317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -19351,8 +19351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -19385,8 +19385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -19419,8 +19419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -19453,8 +19453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -19487,8 +19487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -19523,8 +19523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -19559,8 +19559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -19601,8 +19601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -19639,8 +19639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -19677,8 +19677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -19719,8 +19719,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -19755,8 +19755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -19789,8 +19789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -19825,8 +19825,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -19859,8 +19859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -19897,8 +19897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -19937,8 +19937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -19971,8 +19971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -20005,8 +20005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -20039,8 +20039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -20073,8 +20073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -20107,8 +20107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -20141,8 +20141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -20177,8 +20177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -20215,8 +20215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -20249,8 +20249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -20283,8 +20283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -20317,8 +20317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -20351,8 +20351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -20385,8 +20385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -20419,8 +20419,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -20453,8 +20453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -20487,8 +20487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -20521,8 +20521,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -20555,8 +20555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -20589,8 +20589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -20623,8 +20623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -20661,8 +20661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -20695,8 +20695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -20729,8 +20729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -20763,8 +20763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -20797,8 +20797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -20831,8 +20831,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -20865,8 +20865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -20899,8 +20899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -20933,8 +20933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -20967,8 +20967,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -21001,8 +21001,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -21035,8 +21035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -21069,8 +21069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -21103,8 +21103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -21137,8 +21137,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -21173,8 +21173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -21207,8 +21207,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -21241,8 +21241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -21277,8 +21277,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -21313,8 +21313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -21355,8 +21355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -21391,8 +21391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -21425,8 +21425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -21459,8 +21459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -21493,8 +21493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -21527,8 +21527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -21563,8 +21563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -21597,8 +21597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -21631,8 +21631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -21665,8 +21665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -21699,8 +21699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -21735,8 +21735,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -21775,8 +21775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -21817,8 +21817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -21851,8 +21851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -21889,8 +21889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -21923,8 +21923,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -21963,8 +21963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -21999,8 +21999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -22035,8 +22035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -22071,8 +22071,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -22109,8 +22109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -22143,8 +22143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -22179,8 +22179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -22213,8 +22213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -22247,8 +22247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -22281,8 +22281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -22315,8 +22315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -22349,8 +22349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -22383,8 +22383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -22417,8 +22417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -22451,8 +22451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -22485,8 +22485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -22519,8 +22519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -22555,8 +22555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -22589,8 +22589,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -22623,8 +22623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -22657,8 +22657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -22691,8 +22691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -22725,8 +22725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -22761,8 +22761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -22795,8 +22795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -22829,8 +22829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -22863,8 +22863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -22897,8 +22897,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -22931,8 +22931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -22965,8 +22965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -22999,8 +22999,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -23035,8 +23035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -23077,8 +23077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -23111,8 +23111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -23145,8 +23145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -23179,8 +23179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -23219,8 +23219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -23255,8 +23255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -23291,8 +23291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -23327,8 +23327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -23365,8 +23365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -23399,8 +23399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -23433,8 +23433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -23467,8 +23467,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -23501,8 +23501,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -23535,8 +23535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -23569,8 +23569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -23603,8 +23603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -23637,8 +23637,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -23679,8 +23679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -23713,8 +23713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -23753,8 +23753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -23793,8 +23793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-5-1</v>
       </c>
@@ -23833,8 +23833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-6-1</v>
       </c>
@@ -23873,8 +23873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-7-1</v>
       </c>
@@ -23913,8 +23913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-8-1</v>
       </c>
@@ -23953,8 +23953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-9-1</v>
       </c>
@@ -23993,8 +23993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-10-1</v>
       </c>
@@ -24033,8 +24033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-11-1</v>
       </c>
@@ -24073,8 +24073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-12-1</v>
       </c>
@@ -24113,8 +24113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-13-1</v>
       </c>
@@ -24153,8 +24153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-1</v>
       </c>
@@ -24187,8 +24187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-15-1</v>
       </c>
@@ -24227,8 +24227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-16-1</v>
       </c>
@@ -24261,8 +24261,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-1</v>
       </c>
@@ -24301,8 +24301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-2</v>
       </c>
@@ -24339,8 +24339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-3</v>
       </c>
@@ -24377,8 +24377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-4</v>
       </c>
@@ -24415,8 +24415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-5</v>
       </c>
@@ -24453,8 +24453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-6</v>
       </c>
@@ -24491,8 +24491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-1</v>
       </c>
@@ -24531,8 +24531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-2</v>
       </c>
@@ -24569,8 +24569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-3</v>
       </c>
@@ -24607,8 +24607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-4</v>
       </c>
@@ -24645,8 +24645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-5</v>
       </c>
@@ -24683,8 +24683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-6</v>
       </c>
@@ -24721,8 +24721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-1</v>
       </c>
@@ -24755,8 +24755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-20-1</v>
       </c>
@@ -24789,8 +24789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-21-1</v>
       </c>
@@ -24823,8 +24823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -24859,8 +24859,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F328),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F328)&gt;0)*ROW($F$11:F328),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J328),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -24893,8 +24893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F329),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F329)&gt;0)*ROW($F$11:F329),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J329),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -24935,8 +24935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F330),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F330)&gt;0)*ROW($F$11:F330),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J330),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-2</v>
       </c>
@@ -24973,8 +24973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F331),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F331)&gt;0)*ROW($F$11:F331),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J331),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-3</v>
       </c>
@@ -25011,8 +25011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F332),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F332)&gt;0)*ROW($F$11:F332),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J332),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-4</v>
       </c>
@@ -25049,8 +25049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F333),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F333)&gt;0)*ROW($F$11:F333),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J333),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-5</v>
       </c>
@@ -25087,8 +25087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F334),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F334)&gt;0)*ROW($F$11:F334),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J334),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-6</v>
       </c>
@@ -25125,8 +25125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F335),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F335)&gt;0)*ROW($F$11:F335),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J335),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-7</v>
       </c>
@@ -25163,8 +25163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F336),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F336)&gt;0)*ROW($F$11:F336),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J336),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-8</v>
       </c>
@@ -25201,8 +25201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F337),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F337)&gt;0)*ROW($F$11:F337),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J337),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-1</v>
       </c>
@@ -25241,8 +25241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F338),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F338)&gt;0)*ROW($F$11:F338),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J338),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-2</v>
       </c>
@@ -25279,8 +25279,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F339),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F339)&gt;0)*ROW($F$11:F339),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J339),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-3</v>
       </c>
@@ -25317,8 +25317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F340),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F340)&gt;0)*ROW($F$11:F340),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J340),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-4</v>
       </c>
@@ -25355,8 +25355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F341),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F341)&gt;0)*ROW($F$11:F341),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J341),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -25391,8 +25391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F342),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F342)&gt;0)*ROW($F$11:F342),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J342),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -25427,8 +25427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F343),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F343)&gt;0)*ROW($F$11:F343),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J343),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -25461,8 +25461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F344),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F344)&gt;0)*ROW($F$11:F344),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J344),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -25495,8 +25495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F345),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F345)&gt;0)*ROW($F$11:F345),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J345),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -25529,8 +25529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F346),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F346)&gt;0)*ROW($F$11:F346),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J346),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -25563,8 +25563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F347),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F347)&gt;0)*ROW($F$11:F347),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J347),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -25597,8 +25597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F348),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F348)&gt;0)*ROW($F$11:F348),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J348),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -25631,8 +25631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F349),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F349)&gt;0)*ROW($F$11:F349),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J349),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -25665,8 +25665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F350),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F350)&gt;0)*ROW($F$11:F350),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J350),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -25705,8 +25705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F351),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F351)&gt;0)*ROW($F$11:F351),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J351),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -25747,8 +25747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F352),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F352)&gt;0)*ROW($F$11:F352),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J352),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -25789,8 +25789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F353),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F353)&gt;0)*ROW($F$11:F353),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J353),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -25833,8 +25833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F354),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F354)&gt;0)*ROW($F$11:F354),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J354),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-2</v>
       </c>
@@ -25871,8 +25871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F355),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F355)&gt;0)*ROW($F$11:F355),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J355),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-3</v>
       </c>
@@ -25909,8 +25909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F356),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F356)&gt;0)*ROW($F$11:F356),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J356),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-4</v>
       </c>
@@ -25947,8 +25947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F357),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F357)&gt;0)*ROW($F$11:F357),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J357),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-5</v>
       </c>
@@ -25985,8 +25985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F358),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F358)&gt;0)*ROW($F$11:F358),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J358),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-6</v>
       </c>
@@ -26023,8 +26023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F359),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F359)&gt;0)*ROW($F$11:F359),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J359),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -26059,8 +26059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F360),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F360)&gt;0)*ROW($F$11:F360),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J360),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-2-1</v>
       </c>
@@ -26093,8 +26093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F361),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F361)&gt;0)*ROW($F$11:F361),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J361),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-3-1</v>
       </c>
@@ -26127,8 +26127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F362),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F362)&gt;0)*ROW($F$11:F362),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J362),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-4-1</v>
       </c>
@@ -26161,8 +26161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F363),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F363)&gt;0)*ROW($F$11:F363),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J363),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -26199,8 +26199,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F364),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F364)&gt;0)*ROW($F$11:F364),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J364),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-2-1</v>
       </c>
@@ -26233,8 +26233,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F365),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F365)&gt;0)*ROW($F$11:F365),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J365),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-3-1</v>
       </c>
@@ -26267,8 +26267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F366),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F366)&gt;0)*ROW($F$11:F366),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J366),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-1</v>
       </c>
@@ -26305,8 +26305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F367),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F367)&gt;0)*ROW($F$11:F367),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J367),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-1</v>
       </c>
@@ -26339,8 +26339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F368),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F368)&gt;0)*ROW($F$11:F368),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J368),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-1</v>
       </c>
@@ -26373,8 +26373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F369),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F369)&gt;0)*ROW($F$11:F369),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J369),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-4-1</v>
       </c>
@@ -26407,8 +26407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F370),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F370)&gt;0)*ROW($F$11:F370),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J370),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-5-1</v>
       </c>
@@ -26441,8 +26441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F371),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F371)&gt;0)*ROW($F$11:F371),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J371),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-6-1</v>
       </c>
@@ -26475,8 +26475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F372),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F372)&gt;0)*ROW($F$11:F372),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J372),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-7-1</v>
       </c>
@@ -26509,8 +26509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F373),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F373)&gt;0)*ROW($F$11:F373),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J373),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-8-1</v>
       </c>
@@ -26543,8 +26543,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F374),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F374)&gt;0)*ROW($F$11:F374),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J374),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-9-1</v>
       </c>
@@ -26577,8 +26577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F375),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F375)&gt;0)*ROW($F$11:F375),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J375),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-10-1</v>
       </c>
@@ -26611,8 +26611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F376),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F376)&gt;0)*ROW($F$11:F376),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J376),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-11-1</v>
       </c>
@@ -26645,8 +26645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F377),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F377)&gt;0)*ROW($F$11:F377),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J377),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-12-1</v>
       </c>
@@ -26679,8 +26679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F378),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F378)&gt;0)*ROW($F$11:F378),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J378),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-13-1</v>
       </c>
@@ -26713,8 +26713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F379),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F379)&gt;0)*ROW($F$11:F379),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J379),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-14-1</v>
       </c>
@@ -26747,8 +26747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F380),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F380)&gt;0)*ROW($F$11:F380),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J380),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-1-1</v>
       </c>
@@ -26783,8 +26783,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F381),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F381)&gt;0)*ROW($F$11:F381),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J381),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-2-1</v>
       </c>
@@ -26817,8 +26817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F382),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F382)&gt;0)*ROW($F$11:F382),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J382),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-3-1</v>
       </c>
@@ -26851,8 +26851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F383),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F383)&gt;0)*ROW($F$11:F383),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J383),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-4-1</v>
       </c>
@@ -26885,8 +26885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F384),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F384)&gt;0)*ROW($F$11:F384),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J384),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-5-1</v>
       </c>
@@ -26919,8 +26919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F385),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F385)&gt;0)*ROW($F$11:F385),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J385),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-6-1</v>
       </c>
@@ -26953,8 +26953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F386),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F386)&gt;0)*ROW($F$11:F386),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J386),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-7-1</v>
       </c>
@@ -26987,8 +26987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F387),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F387)&gt;0)*ROW($F$11:F387),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J387),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-1-1</v>
       </c>
@@ -27029,8 +27029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F388),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F388)&gt;0)*ROW($F$11:F388),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J388),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-2-1</v>
       </c>
@@ -27063,8 +27063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F389),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F389)&gt;0)*ROW($F$11:F389),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J389),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-3-1</v>
       </c>
@@ -27097,8 +27097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F390),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F390)&gt;0)*ROW($F$11:F390),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J390),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-4-1</v>
       </c>
@@ -27131,8 +27131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F391),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F391)&gt;0)*ROW($F$11:F391),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J391),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-5-1</v>
       </c>
@@ -27165,8 +27165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F392),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F392)&gt;0)*ROW($F$11:F392),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J392),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-1-1</v>
       </c>
@@ -27203,8 +27203,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F393),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F393)&gt;0)*ROW($F$11:F393),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J393),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-2-1</v>
       </c>
@@ -27237,8 +27237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F394),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F394)&gt;0)*ROW($F$11:F394),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J394),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-3-1</v>
       </c>
@@ -27271,8 +27271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F395),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F395)&gt;0)*ROW($F$11:F395),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J395),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-4-1</v>
       </c>
@@ -27305,8 +27305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F396),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F396)&gt;0)*ROW($F$11:F396),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J396),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-5-1</v>
       </c>
@@ -27339,8 +27339,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F397),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F397)&gt;0)*ROW($F$11:F397),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J397),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-1</v>
       </c>
@@ -27385,8 +27385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F398),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F398)&gt;0)*ROW($F$11:F398),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J398),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-2</v>
       </c>
@@ -27423,8 +27423,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F399),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F399)&gt;0)*ROW($F$11:F399),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J399),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-3</v>
       </c>
@@ -27461,8 +27461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F400),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F400)&gt;0)*ROW($F$11:F400),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J400),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-4</v>
       </c>
@@ -27499,8 +27499,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F401),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F401)&gt;0)*ROW($F$11:F401),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J401),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-5</v>
       </c>
@@ -27537,8 +27537,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F402),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F402)&gt;0)*ROW($F$11:F402),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J402),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-6</v>
       </c>
@@ -27575,8 +27575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F403),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F403)&gt;0)*ROW($F$11:F403),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J403),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-2-1</v>
       </c>
@@ -27609,8 +27609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F404),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F404)&gt;0)*ROW($F$11:F404),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J404),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-1</v>
       </c>
@@ -27649,8 +27649,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F405),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F405)&gt;0)*ROW($F$11:F405),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J405),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-2</v>
       </c>
@@ -27687,8 +27687,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F406),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F406)&gt;0)*ROW($F$11:F406),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J406),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-3</v>
       </c>
@@ -27725,8 +27725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F407),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F407)&gt;0)*ROW($F$11:F407),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J407),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-4</v>
       </c>
@@ -27763,8 +27763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F408),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F408)&gt;0)*ROW($F$11:F408),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J408),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-5</v>
       </c>
@@ -27801,8 +27801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F409),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F409)&gt;0)*ROW($F$11:F409),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J409),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-6</v>
       </c>
@@ -27839,8 +27839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F410),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F410)&gt;0)*ROW($F$11:F410),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J410),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-4-1</v>
       </c>
@@ -27873,8 +27873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F411),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F411)&gt;0)*ROW($F$11:F411),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J411),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-5-1</v>
       </c>
@@ -27907,8 +27907,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F412),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F412)&gt;0)*ROW($F$11:F412),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J412),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-6-1</v>
       </c>
@@ -27941,8 +27941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F413),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F413)&gt;0)*ROW($F$11:F413),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J413),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>116-1-1</v>
       </c>
@@ -27985,8 +27985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F414),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F414)&gt;0)*ROW($F$11:F414),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J414),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-1</v>
       </c>
@@ -28029,8 +28029,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F415),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F415)&gt;0)*ROW($F$11:F415),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J415),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-2</v>
       </c>
@@ -28067,8 +28067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F416),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F416)&gt;0)*ROW($F$11:F416),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J416),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-3</v>
       </c>
@@ -28105,8 +28105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F417),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F417)&gt;0)*ROW($F$11:F417),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J417),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-4</v>
       </c>
@@ -28143,8 +28143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F418),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F418)&gt;0)*ROW($F$11:F418),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J418),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-5</v>
       </c>
@@ -28181,8 +28181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F419),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F419)&gt;0)*ROW($F$11:F419),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J419),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-6</v>
       </c>
@@ -28219,8 +28219,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F420),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F420)&gt;0)*ROW($F$11:F420),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J420),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-7</v>
       </c>
@@ -28257,8 +28257,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F421),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F421)&gt;0)*ROW($F$11:F421),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J421),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>118-1-1</v>
       </c>
@@ -28301,8 +28301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F422),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F422)&gt;0)*ROW($F$11:F422),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J422),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-1-1</v>
       </c>
@@ -28343,8 +28343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F423),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F423)&gt;0)*ROW($F$11:F423),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J423),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-2-1</v>
       </c>
@@ -28527,11 +28527,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D11),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -28563,11 +28563,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D12),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -28595,11 +28595,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D13),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -28629,11 +28629,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D14),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -28661,11 +28661,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D15),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -28695,11 +28695,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D16),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -28729,11 +28729,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D17),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -28763,11 +28763,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D18),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -28797,11 +28797,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D19),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -28833,11 +28833,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D20),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -28867,11 +28867,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D21),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D21)&gt;0)*ROW($D$11:D21),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E21),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E21)&gt;0)*ROW($E$11:E21),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -28901,11 +28901,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D22),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D22)&gt;0)*ROW($D$11:D22),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E22),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E22)&gt;0)*ROW($E$11:E22),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -28937,11 +28937,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D23),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D23)&gt;0)*ROW($D$11:D23),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E23),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E23)&gt;0)*ROW($E$11:E23),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -28971,11 +28971,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D24),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D24)&gt;0)*ROW($D$11:D24),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E24),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E24)&gt;0)*ROW($E$11:E24),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -29007,11 +29007,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D25),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D25)&gt;0)*ROW($D$11:D25),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E25),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E25)&gt;0)*ROW($E$11:E25),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -29039,11 +29039,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D26),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D26)&gt;0)*ROW($D$11:D26),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E26),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E26)&gt;0)*ROW($E$11:E26),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -29073,11 +29073,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D27),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D27)&gt;0)*ROW($D$11:D27),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E27),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E27)&gt;0)*ROW($E$11:E27),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -29105,11 +29105,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D28),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D28)&gt;0)*ROW($D$11:D28),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E28),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E28)&gt;0)*ROW($E$11:E28),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -29143,11 +29143,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D29),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D29)&gt;0)*ROW($D$11:D29),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E29),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E29)&gt;0)*ROW($E$11:E29),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
